--- a/entregables/COTIZACION_PRECIOS_ACU_TAPA_REGISTRO_HOGAR_REFUGIO.xlsx
+++ b/entregables/COTIZACION_PRECIOS_ACU_TAPA_REGISTRO_HOGAR_REFUGIO.xlsx
@@ -95,7 +95,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -117,11 +117,55 @@
         <color rgb="00808080"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00808080"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00808080"/>
+      </right>
+      <top style="thin">
+        <color rgb="00808080"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00808080"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00808080"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00808080"/>
+      </right>
+      <top style="thin">
+        <color rgb="00808080"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00808080"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -220,6 +264,8 @@
     <xf numFmtId="4" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -610,19 +656,19 @@
           <t>COTIZACION DE INSUMOS - ACU TAPA DE REGISTRO 0.68 x 0.68 C/MARCO Y CONTRAMARCO (Delphin 01.04.04.06.05.01; metrado 01.04.04.05.01)</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="2" t="n"/>
-      <c r="K1" s="2" t="n"/>
-      <c r="L1" s="2" t="n"/>
-      <c r="M1" s="2" t="n"/>
-      <c r="N1" s="2" t="n"/>
+      <c r="B1" s="34" t="n"/>
+      <c r="C1" s="34" t="n"/>
+      <c r="D1" s="34" t="n"/>
+      <c r="E1" s="34" t="n"/>
+      <c r="F1" s="34" t="n"/>
+      <c r="G1" s="34" t="n"/>
+      <c r="H1" s="34" t="n"/>
+      <c r="I1" s="34" t="n"/>
+      <c r="J1" s="34" t="n"/>
+      <c r="K1" s="34" t="n"/>
+      <c r="L1" s="34" t="n"/>
+      <c r="M1" s="34" t="n"/>
+      <c r="N1" s="35" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -630,19 +676,19 @@
           <t>PROYECTO: HOGAR DE REFUGIO TEMPORAL - MUJERES VIOLENTADAS, DISTRITO DE MORALES, SAN MARTIN - CUI N.° 2675514</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
-      <c r="G2" s="2" t="n"/>
-      <c r="H2" s="2" t="n"/>
-      <c r="I2" s="2" t="n"/>
-      <c r="J2" s="2" t="n"/>
-      <c r="K2" s="2" t="n"/>
-      <c r="L2" s="2" t="n"/>
-      <c r="M2" s="2" t="n"/>
-      <c r="N2" s="2" t="n"/>
+      <c r="B2" s="34" t="n"/>
+      <c r="C2" s="34" t="n"/>
+      <c r="D2" s="34" t="n"/>
+      <c r="E2" s="34" t="n"/>
+      <c r="F2" s="34" t="n"/>
+      <c r="G2" s="34" t="n"/>
+      <c r="H2" s="34" t="n"/>
+      <c r="I2" s="34" t="n"/>
+      <c r="J2" s="34" t="n"/>
+      <c r="K2" s="34" t="n"/>
+      <c r="L2" s="34" t="n"/>
+      <c r="M2" s="34" t="n"/>
+      <c r="N2" s="35" t="n"/>
     </row>
     <row r="3" ht="42" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
@@ -650,20 +696,21 @@
           <t>Busqueda de precios publicados: 14/10/2026. Precio publicado tal como lo muestra la tienda (con IGV, salvo la tarifa de agua). Precio sin IGV = precio publicado / contenido / factor IGV. Los precios de Sodimac y Promart son nacionales (ambas tienen tienda en Tarapoto); el precio de la tienda de Tarapoto puede variar.</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-      <c r="F3" s="2" t="n"/>
-      <c r="G3" s="2" t="n"/>
-      <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="n"/>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n"/>
-    </row>
+      <c r="B3" s="34" t="n"/>
+      <c r="C3" s="34" t="n"/>
+      <c r="D3" s="34" t="n"/>
+      <c r="E3" s="34" t="n"/>
+      <c r="F3" s="34" t="n"/>
+      <c r="G3" s="34" t="n"/>
+      <c r="H3" s="34" t="n"/>
+      <c r="I3" s="34" t="n"/>
+      <c r="J3" s="34" t="n"/>
+      <c r="K3" s="34" t="n"/>
+      <c r="L3" s="34" t="n"/>
+      <c r="M3" s="34" t="n"/>
+      <c r="N3" s="35" t="n"/>
+    </row>
+    <row r="4"/>
     <row r="5" ht="42" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
@@ -1934,7 +1981,7 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Jornal basico 2026 S/ 89.30 por dia (convenio CAPECO-FTCCP 2026, R.M. 197-2025-TR); costo hora-hombre con beneficios sociales de la planilla</t>
+          <t>Jornal basico 2026 S/ 89.30 por dia (convenio CAPECO-FTCCP 2026, R.M. 197-2025-TR); costo hora-hombre 2026 de la hoja COSTO HORA HOMBRE 2026 de la planilla</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -1943,7 +1990,7 @@
         </is>
       </c>
       <c r="F26" s="6" t="n">
-        <v>30.42</v>
+        <v>29.3</v>
       </c>
       <c r="G26" s="18" t="n">
         <v>1</v>
@@ -1956,7 +2003,7 @@
         <v/>
       </c>
       <c r="J26" s="9" t="n">
-        <v>30.42</v>
+        <v>29.3</v>
       </c>
       <c r="K26" s="10">
         <f>I26/J26-1</f>
@@ -1972,9 +2019,9 @@
           <t>abrir</t>
         </is>
       </c>
-      <c r="N26" s="16" t="inlineStr">
-        <is>
-          <t>JORNAL OFICIAL 2026; costo hh se mantiene (decision pendiente)</t>
+      <c r="N26" s="12" t="inlineStr">
+        <is>
+          <t>JORNAL OFICIAL 2026; costo hh 2026 = costo CAPECO 2024-2025 x jornal 2026 / jornal 2024-2025</t>
         </is>
       </c>
     </row>
@@ -1994,7 +2041,7 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Jornal basico 2026 S/ 69.75 por dia (convenio CAPECO-FTCCP 2026, R.M. 197-2025-TR); costo hora-hombre con beneficios sociales de la planilla</t>
+          <t>Jornal basico 2026 S/ 69.75 por dia (convenio CAPECO-FTCCP 2026, R.M. 197-2025-TR); costo hora-hombre 2026 de la hoja COSTO HORA HOMBRE 2026 de la planilla</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -2032,9 +2079,9 @@
           <t>abrir</t>
         </is>
       </c>
-      <c r="N27" s="16" t="inlineStr">
-        <is>
-          <t>JORNAL OFICIAL 2026; costo hh se mantiene (decision pendiente)</t>
+      <c r="N27" s="12" t="inlineStr">
+        <is>
+          <t>JORNAL OFICIAL 2026; costo hh 2026 = costo CAPECO 2024-2025 x jornal 2026 / jornal 2024-2025</t>
         </is>
       </c>
     </row>
@@ -2054,7 +2101,7 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Jornal basico 2026 S/ 62.80 por dia (convenio CAPECO-FTCCP 2026, R.M. 197-2025-TR); costo hora-hombre con beneficios sociales de la planilla</t>
+          <t>Jornal basico 2026 S/ 62.80 por dia (convenio CAPECO-FTCCP 2026, R.M. 197-2025-TR); costo hora-hombre 2026 de la hoja COSTO HORA HOMBRE 2026 de la planilla</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -2092,31 +2139,32 @@
           <t>abrir</t>
         </is>
       </c>
-      <c r="N28" s="16" t="inlineStr">
-        <is>
-          <t>JORNAL OFICIAL 2026; costo hh se mantiene (decision pendiente)</t>
-        </is>
-      </c>
-    </row>
+      <c r="N28" s="12" t="inlineStr">
+        <is>
+          <t>JORNAL OFICIAL 2026; costo hh 2026 = costo CAPECO 2024-2025 x jornal 2026 / jornal 2024-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="19" t="inlineStr">
         <is>
           <t>NOTAS</t>
         </is>
       </c>
-      <c r="B30" s="2" t="n"/>
-      <c r="C30" s="2" t="n"/>
-      <c r="D30" s="2" t="n"/>
-      <c r="E30" s="2" t="n"/>
-      <c r="F30" s="2" t="n"/>
-      <c r="G30" s="2" t="n"/>
-      <c r="H30" s="2" t="n"/>
-      <c r="I30" s="2" t="n"/>
-      <c r="J30" s="2" t="n"/>
-      <c r="K30" s="2" t="n"/>
-      <c r="L30" s="2" t="n"/>
-      <c r="M30" s="2" t="n"/>
-      <c r="N30" s="2" t="n"/>
+      <c r="B30" s="34" t="n"/>
+      <c r="C30" s="34" t="n"/>
+      <c r="D30" s="34" t="n"/>
+      <c r="E30" s="34" t="n"/>
+      <c r="F30" s="34" t="n"/>
+      <c r="G30" s="34" t="n"/>
+      <c r="H30" s="34" t="n"/>
+      <c r="I30" s="34" t="n"/>
+      <c r="J30" s="34" t="n"/>
+      <c r="K30" s="34" t="n"/>
+      <c r="L30" s="34" t="n"/>
+      <c r="M30" s="34" t="n"/>
+      <c r="N30" s="35" t="n"/>
     </row>
     <row r="31" ht="28" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
@@ -2124,19 +2172,19 @@
           <t>1. Verde = precio publicado y encontrado; naranja = referencia (otra ciudad o sin ciudad); rojo = sin precio publicado: se mantiene el precio actual y debe cotizarse en Tarapoto.</t>
         </is>
       </c>
-      <c r="B31" s="2" t="n"/>
-      <c r="C31" s="2" t="n"/>
-      <c r="D31" s="2" t="n"/>
-      <c r="E31" s="2" t="n"/>
-      <c r="F31" s="2" t="n"/>
-      <c r="G31" s="2" t="n"/>
-      <c r="H31" s="2" t="n"/>
-      <c r="I31" s="2" t="n"/>
-      <c r="J31" s="2" t="n"/>
-      <c r="K31" s="2" t="n"/>
-      <c r="L31" s="2" t="n"/>
-      <c r="M31" s="2" t="n"/>
-      <c r="N31" s="2" t="n"/>
+      <c r="B31" s="34" t="n"/>
+      <c r="C31" s="34" t="n"/>
+      <c r="D31" s="34" t="n"/>
+      <c r="E31" s="34" t="n"/>
+      <c r="F31" s="34" t="n"/>
+      <c r="G31" s="34" t="n"/>
+      <c r="H31" s="34" t="n"/>
+      <c r="I31" s="34" t="n"/>
+      <c r="J31" s="34" t="n"/>
+      <c r="K31" s="34" t="n"/>
+      <c r="L31" s="34" t="n"/>
+      <c r="M31" s="34" t="n"/>
+      <c r="N31" s="35" t="n"/>
     </row>
     <row r="32" ht="28" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
@@ -2144,19 +2192,19 @@
           <t>2. Angulo L 2"x2"x3/16": ninguna tienda en linea del Peru lo publica en soles; solo se vende por pedido a distribuidores. Por eso se propone el L 1 1/2"x1 1/2"x1/8" (hoja 2 ANGULOS).</t>
         </is>
       </c>
-      <c r="B32" s="2" t="n"/>
-      <c r="C32" s="2" t="n"/>
-      <c r="D32" s="2" t="n"/>
-      <c r="E32" s="2" t="n"/>
-      <c r="F32" s="2" t="n"/>
-      <c r="G32" s="2" t="n"/>
-      <c r="H32" s="2" t="n"/>
-      <c r="I32" s="2" t="n"/>
-      <c r="J32" s="2" t="n"/>
-      <c r="K32" s="2" t="n"/>
-      <c r="L32" s="2" t="n"/>
-      <c r="M32" s="2" t="n"/>
-      <c r="N32" s="2" t="n"/>
+      <c r="B32" s="34" t="n"/>
+      <c r="C32" s="34" t="n"/>
+      <c r="D32" s="34" t="n"/>
+      <c r="E32" s="34" t="n"/>
+      <c r="F32" s="34" t="n"/>
+      <c r="G32" s="34" t="n"/>
+      <c r="H32" s="34" t="n"/>
+      <c r="I32" s="34" t="n"/>
+      <c r="J32" s="34" t="n"/>
+      <c r="K32" s="34" t="n"/>
+      <c r="L32" s="34" t="n"/>
+      <c r="M32" s="34" t="n"/>
+      <c r="N32" s="35" t="n"/>
     </row>
     <row r="33" ht="28" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
@@ -2164,19 +2212,19 @@
           <t>3. Piedra chancada 1/2": en Tarapoto se publica la de 3/4" (S/ 70.00 el m3, Agregados Tarapoto, Morales); la de 1/2" debe cotizarse. En la tapa (8 cm) su incidencia es menor de S/ 2.00.</t>
         </is>
       </c>
-      <c r="B33" s="2" t="n"/>
-      <c r="C33" s="2" t="n"/>
-      <c r="D33" s="2" t="n"/>
-      <c r="E33" s="2" t="n"/>
-      <c r="F33" s="2" t="n"/>
-      <c r="G33" s="2" t="n"/>
-      <c r="H33" s="2" t="n"/>
-      <c r="I33" s="2" t="n"/>
-      <c r="J33" s="2" t="n"/>
-      <c r="K33" s="2" t="n"/>
-      <c r="L33" s="2" t="n"/>
-      <c r="M33" s="2" t="n"/>
-      <c r="N33" s="2" t="n"/>
+      <c r="B33" s="34" t="n"/>
+      <c r="C33" s="34" t="n"/>
+      <c r="D33" s="34" t="n"/>
+      <c r="E33" s="34" t="n"/>
+      <c r="F33" s="34" t="n"/>
+      <c r="G33" s="34" t="n"/>
+      <c r="H33" s="34" t="n"/>
+      <c r="I33" s="34" t="n"/>
+      <c r="J33" s="34" t="n"/>
+      <c r="K33" s="34" t="n"/>
+      <c r="L33" s="34" t="n"/>
+      <c r="M33" s="34" t="n"/>
+      <c r="N33" s="35" t="n"/>
     </row>
     <row r="34" ht="28" customHeight="1">
       <c r="A34" s="3" t="inlineStr">
@@ -2184,19 +2232,19 @@
           <t>4. Arena (Agregados Tarapoto): se tomo el precio publicado como precio con IGV; si el proveedor no emite factura, usar S/ 48.00 directo (celda H11 = 1.00).</t>
         </is>
       </c>
-      <c r="B34" s="2" t="n"/>
-      <c r="C34" s="2" t="n"/>
-      <c r="D34" s="2" t="n"/>
-      <c r="E34" s="2" t="n"/>
-      <c r="F34" s="2" t="n"/>
-      <c r="G34" s="2" t="n"/>
-      <c r="H34" s="2" t="n"/>
-      <c r="I34" s="2" t="n"/>
-      <c r="J34" s="2" t="n"/>
-      <c r="K34" s="2" t="n"/>
-      <c r="L34" s="2" t="n"/>
-      <c r="M34" s="2" t="n"/>
-      <c r="N34" s="2" t="n"/>
+      <c r="B34" s="34" t="n"/>
+      <c r="C34" s="34" t="n"/>
+      <c r="D34" s="34" t="n"/>
+      <c r="E34" s="34" t="n"/>
+      <c r="F34" s="34" t="n"/>
+      <c r="G34" s="34" t="n"/>
+      <c r="H34" s="34" t="n"/>
+      <c r="I34" s="34" t="n"/>
+      <c r="J34" s="34" t="n"/>
+      <c r="K34" s="34" t="n"/>
+      <c r="L34" s="34" t="n"/>
+      <c r="M34" s="34" t="n"/>
+      <c r="N34" s="35" t="n"/>
     </row>
     <row r="35" ht="28" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
@@ -2204,39 +2252,39 @@
           <t>5. Lija y thinner reemplazan al global "Lija y thinner" de la ACU actual (ver DESAGREGADO_LIJA_THINNER_TAPA_REGISTRO_HOGAR_REFUGIO.xlsx).</t>
         </is>
       </c>
-      <c r="B35" s="2" t="n"/>
-      <c r="C35" s="2" t="n"/>
-      <c r="D35" s="2" t="n"/>
-      <c r="E35" s="2" t="n"/>
-      <c r="F35" s="2" t="n"/>
-      <c r="G35" s="2" t="n"/>
-      <c r="H35" s="2" t="n"/>
-      <c r="I35" s="2" t="n"/>
-      <c r="J35" s="2" t="n"/>
-      <c r="K35" s="2" t="n"/>
-      <c r="L35" s="2" t="n"/>
-      <c r="M35" s="2" t="n"/>
-      <c r="N35" s="2" t="n"/>
+      <c r="B35" s="34" t="n"/>
+      <c r="C35" s="34" t="n"/>
+      <c r="D35" s="34" t="n"/>
+      <c r="E35" s="34" t="n"/>
+      <c r="F35" s="34" t="n"/>
+      <c r="G35" s="34" t="n"/>
+      <c r="H35" s="34" t="n"/>
+      <c r="I35" s="34" t="n"/>
+      <c r="J35" s="34" t="n"/>
+      <c r="K35" s="34" t="n"/>
+      <c r="L35" s="34" t="n"/>
+      <c r="M35" s="34" t="n"/>
+      <c r="N35" s="35" t="n"/>
     </row>
     <row r="36" ht="28" customHeight="1">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>6. Mano de obra: el jornal basico 2026 es oficial; el costo hora-hombre con beneficios sociales de la planilla (30.42 / 22.95 / 20.79) no se cambia en esta propuesta.</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="n"/>
-      <c r="C36" s="2" t="n"/>
-      <c r="D36" s="2" t="n"/>
-      <c r="E36" s="2" t="n"/>
-      <c r="F36" s="2" t="n"/>
-      <c r="G36" s="2" t="n"/>
-      <c r="H36" s="2" t="n"/>
-      <c r="I36" s="2" t="n"/>
-      <c r="J36" s="2" t="n"/>
-      <c r="K36" s="2" t="n"/>
-      <c r="L36" s="2" t="n"/>
-      <c r="M36" s="2" t="n"/>
-      <c r="N36" s="2" t="n"/>
+          <t>6. Mano de obra 2026: jornal basico oficial (R.M. 197-2025-TR) y costo hora-hombre 29.30 / 22.95 / 20.79 de la hoja COSTO HORA HOMBRE 2026 de la planilla (costo CAPECO 2024-2025 llevado al jornal 2026).</t>
+        </is>
+      </c>
+      <c r="B36" s="34" t="n"/>
+      <c r="C36" s="34" t="n"/>
+      <c r="D36" s="34" t="n"/>
+      <c r="E36" s="34" t="n"/>
+      <c r="F36" s="34" t="n"/>
+      <c r="G36" s="34" t="n"/>
+      <c r="H36" s="34" t="n"/>
+      <c r="I36" s="34" t="n"/>
+      <c r="J36" s="34" t="n"/>
+      <c r="K36" s="34" t="n"/>
+      <c r="L36" s="34" t="n"/>
+      <c r="M36" s="34" t="n"/>
+      <c r="N36" s="35" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -2304,13 +2352,13 @@
           <t>PROPUESTA DE ANGULOS PARA MARCO Y CONTRAMARCO - TAPA DE REGISTRO 0.68 x 0.68 x 0.08 (DD-01, DD-02, DP-06B)</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
+      <c r="B1" s="34" t="n"/>
+      <c r="C1" s="34" t="n"/>
+      <c r="D1" s="34" t="n"/>
+      <c r="E1" s="34" t="n"/>
+      <c r="F1" s="34" t="n"/>
+      <c r="G1" s="34" t="n"/>
+      <c r="H1" s="35" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -2318,13 +2366,13 @@
           <t>PROYECTO: HOGAR DE REFUGIO TEMPORAL - MUJERES VIOLENTADAS, DISTRITO DE MORALES, SAN MARTIN - CUI N.° 2675514</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
-      <c r="G2" s="2" t="n"/>
-      <c r="H2" s="2" t="n"/>
+      <c r="B2" s="34" t="n"/>
+      <c r="C2" s="34" t="n"/>
+      <c r="D2" s="34" t="n"/>
+      <c r="E2" s="34" t="n"/>
+      <c r="F2" s="34" t="n"/>
+      <c r="G2" s="34" t="n"/>
+      <c r="H2" s="35" t="n"/>
     </row>
     <row r="3" ht="42" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
@@ -2332,27 +2380,28 @@
           <t>Los 10 registros (RS-01 a RS-07, CL y 2 en CC) estan fuera del ingreso vehicular OE-01 (prog. 0+026.32 a 0+031.33) y del porton de motos (0+039.04 a 0+041.04), bajo vereda y jardin: carga peatonal (E.020). El RS-03 (0+032.50) y el RS-04 (0+042.68) son los mas cercanos a los cruces.</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-      <c r="F3" s="2" t="n"/>
-      <c r="G3" s="2" t="n"/>
-      <c r="H3" s="2" t="n"/>
-    </row>
+      <c r="B3" s="34" t="n"/>
+      <c r="C3" s="34" t="n"/>
+      <c r="D3" s="34" t="n"/>
+      <c r="E3" s="34" t="n"/>
+      <c r="F3" s="34" t="n"/>
+      <c r="G3" s="34" t="n"/>
+      <c r="H3" s="35" t="n"/>
+    </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="19" t="inlineStr">
         <is>
           <t>1. ANGULOS COMERCIALES (barra de 6 m, ASTM A36)</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n"/>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="n"/>
-      <c r="F5" s="2" t="n"/>
-      <c r="G5" s="2" t="n"/>
-      <c r="H5" s="2" t="n"/>
+      <c r="B5" s="34" t="n"/>
+      <c r="C5" s="34" t="n"/>
+      <c r="D5" s="34" t="n"/>
+      <c r="E5" s="34" t="n"/>
+      <c r="F5" s="34" t="n"/>
+      <c r="G5" s="34" t="n"/>
+      <c r="H5" s="35" t="n"/>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -2562,19 +2611,20 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="19" t="inlineStr">
         <is>
           <t>2. VERIFICACION DEL CONTRAMARCO CON L 1 1/2"x1 1/2"x1/8" (carga peatonal)</t>
         </is>
       </c>
-      <c r="B13" s="2" t="n"/>
-      <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="n"/>
-      <c r="E13" s="2" t="n"/>
-      <c r="F13" s="2" t="n"/>
-      <c r="G13" s="2" t="n"/>
-      <c r="H13" s="2" t="n"/>
+      <c r="B13" s="34" t="n"/>
+      <c r="C13" s="34" t="n"/>
+      <c r="D13" s="34" t="n"/>
+      <c r="E13" s="34" t="n"/>
+      <c r="F13" s="34" t="n"/>
+      <c r="G13" s="34" t="n"/>
+      <c r="H13" s="35" t="n"/>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
@@ -3037,19 +3087,20 @@
       <c r="G31" s="5" t="n"/>
       <c r="H31" s="3" t="inlineStr"/>
     </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" s="19" t="inlineStr">
         <is>
           <t>3. CONCLUSION</t>
         </is>
       </c>
-      <c r="B33" s="2" t="n"/>
-      <c r="C33" s="2" t="n"/>
-      <c r="D33" s="2" t="n"/>
-      <c r="E33" s="2" t="n"/>
-      <c r="F33" s="2" t="n"/>
-      <c r="G33" s="2" t="n"/>
-      <c r="H33" s="2" t="n"/>
+      <c r="B33" s="34" t="n"/>
+      <c r="C33" s="34" t="n"/>
+      <c r="D33" s="34" t="n"/>
+      <c r="E33" s="34" t="n"/>
+      <c r="F33" s="34" t="n"/>
+      <c r="G33" s="34" t="n"/>
+      <c r="H33" s="35" t="n"/>
     </row>
     <row r="34" ht="40" customHeight="1">
       <c r="A34" s="3" t="inlineStr">
@@ -3057,13 +3108,13 @@
           <t>El ala horizontal del contramarco descansa entera sobre el concreto del borde engrosado, de modo que el angulo no trabaja a flexion: protege la arista y sirve de asiento. El espesor de 3/16" no aporta resistencia necesaria; con 1/8" el esfuerzo de apoyo es muy inferior al admisible.</t>
         </is>
       </c>
-      <c r="B34" s="2" t="n"/>
-      <c r="C34" s="2" t="n"/>
-      <c r="D34" s="2" t="n"/>
-      <c r="E34" s="2" t="n"/>
-      <c r="F34" s="2" t="n"/>
-      <c r="G34" s="2" t="n"/>
-      <c r="H34" s="2" t="n"/>
+      <c r="B34" s="34" t="n"/>
+      <c r="C34" s="34" t="n"/>
+      <c r="D34" s="34" t="n"/>
+      <c r="E34" s="34" t="n"/>
+      <c r="F34" s="34" t="n"/>
+      <c r="G34" s="34" t="n"/>
+      <c r="H34" s="35" t="n"/>
     </row>
     <row r="35" ht="40" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
@@ -3071,13 +3122,13 @@
           <t>Se propone un solo angulo L 1 1/2"x1 1/2"x1/8" para marco y contramarco: precio publicado, una barra de 6 m por tapa, menos peso (10.10 kg en lugar de 15.14 kg por tapa) y mayor luz libre.</t>
         </is>
       </c>
-      <c r="B35" s="2" t="n"/>
-      <c r="C35" s="2" t="n"/>
-      <c r="D35" s="2" t="n"/>
-      <c r="E35" s="2" t="n"/>
-      <c r="F35" s="2" t="n"/>
-      <c r="G35" s="2" t="n"/>
-      <c r="H35" s="2" t="n"/>
+      <c r="B35" s="34" t="n"/>
+      <c r="C35" s="34" t="n"/>
+      <c r="D35" s="34" t="n"/>
+      <c r="E35" s="34" t="n"/>
+      <c r="F35" s="34" t="n"/>
+      <c r="G35" s="34" t="n"/>
+      <c r="H35" s="35" t="n"/>
     </row>
     <row r="36" ht="40" customHeight="1">
       <c r="A36" s="3" t="inlineStr">
@@ -3085,13 +3136,13 @@
           <t>Al usar ala de 1 1/2", el asiento de concreto bajo el ala horizontal pasa de 50 mm a 38 mm. Los anclajes 3/8" se sueldan al ala vertical con cordon de 1/8" (espesor del angulo 3.2 mm).</t>
         </is>
       </c>
-      <c r="B36" s="2" t="n"/>
-      <c r="C36" s="2" t="n"/>
-      <c r="D36" s="2" t="n"/>
-      <c r="E36" s="2" t="n"/>
-      <c r="F36" s="2" t="n"/>
-      <c r="G36" s="2" t="n"/>
-      <c r="H36" s="2" t="n"/>
+      <c r="B36" s="34" t="n"/>
+      <c r="C36" s="34" t="n"/>
+      <c r="D36" s="34" t="n"/>
+      <c r="E36" s="34" t="n"/>
+      <c r="F36" s="34" t="n"/>
+      <c r="G36" s="34" t="n"/>
+      <c r="H36" s="35" t="n"/>
     </row>
     <row r="37" ht="40" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
@@ -3099,13 +3150,13 @@
           <t>Si se aprueba, cambian: COLECTOR PARAMETROS (fila 36, 38 y 40), COLECTOR REGISTROS Y TAPAS (fila 23), DESAGREGADO TAPA REGISTRO, ACU TAPA REGISTRO, la descripcion de la planilla general (fila 317) y las laminas DD-01, DD-02, DP-06B y cuadros. Angulos de la partida: de 151.42 kg a 101.02 kg (10 tapas).</t>
         </is>
       </c>
-      <c r="B37" s="2" t="n"/>
-      <c r="C37" s="2" t="n"/>
-      <c r="D37" s="2" t="n"/>
-      <c r="E37" s="2" t="n"/>
-      <c r="F37" s="2" t="n"/>
-      <c r="G37" s="2" t="n"/>
-      <c r="H37" s="2" t="n"/>
+      <c r="B37" s="34" t="n"/>
+      <c r="C37" s="34" t="n"/>
+      <c r="D37" s="34" t="n"/>
+      <c r="E37" s="34" t="n"/>
+      <c r="F37" s="34" t="n"/>
+      <c r="G37" s="34" t="n"/>
+      <c r="H37" s="35" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -3152,15 +3203,15 @@
           <t>ACU TAPA DE REGISTRO 0.68 x 0.68 C/MARCO Y CONTRAMARCO - ACTUAL FRENTE A PROPUESTA CON PRECIOS COTIZADOS (por und de tapa)</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="2" t="n"/>
+      <c r="B1" s="34" t="n"/>
+      <c r="C1" s="34" t="n"/>
+      <c r="D1" s="34" t="n"/>
+      <c r="E1" s="34" t="n"/>
+      <c r="F1" s="34" t="n"/>
+      <c r="G1" s="34" t="n"/>
+      <c r="H1" s="34" t="n"/>
+      <c r="I1" s="34" t="n"/>
+      <c r="J1" s="35" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -3168,15 +3219,15 @@
           <t>PROYECTO: HOGAR DE REFUGIO TEMPORAL - MUJERES VIOLENTADAS, DISTRITO DE MORALES, SAN MARTIN - CUI N.° 2675514</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
-      <c r="G2" s="2" t="n"/>
-      <c r="H2" s="2" t="n"/>
-      <c r="I2" s="2" t="n"/>
-      <c r="J2" s="2" t="n"/>
+      <c r="B2" s="34" t="n"/>
+      <c r="C2" s="34" t="n"/>
+      <c r="D2" s="34" t="n"/>
+      <c r="E2" s="34" t="n"/>
+      <c r="F2" s="34" t="n"/>
+      <c r="G2" s="34" t="n"/>
+      <c r="H2" s="34" t="n"/>
+      <c r="I2" s="34" t="n"/>
+      <c r="J2" s="35" t="n"/>
     </row>
     <row r="3" ht="42" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
@@ -3184,31 +3235,32 @@
           <t>Actual = ACU TAPA REGISTRO de la planilla vigente. Propuesta = marco y contramarco con L 1 1/2"x1 1/2"x1/8", lija y thinner desagregados y precios de la hoja 1 COTIZACION. Ratios de COLECTOR INSUMOS sin cambio. Mano de obra con el costo hora-hombre de la planilla.</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-      <c r="F3" s="2" t="n"/>
-      <c r="G3" s="2" t="n"/>
-      <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-    </row>
+      <c r="B3" s="34" t="n"/>
+      <c r="C3" s="34" t="n"/>
+      <c r="D3" s="34" t="n"/>
+      <c r="E3" s="34" t="n"/>
+      <c r="F3" s="34" t="n"/>
+      <c r="G3" s="34" t="n"/>
+      <c r="H3" s="34" t="n"/>
+      <c r="I3" s="34" t="n"/>
+      <c r="J3" s="35" t="n"/>
+    </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="19" t="inlineStr">
         <is>
           <t>PARAMETROS DE LA PROPUESTA (por tapa)</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n"/>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="n"/>
-      <c r="F5" s="2" t="n"/>
-      <c r="G5" s="2" t="n"/>
-      <c r="H5" s="2" t="n"/>
-      <c r="I5" s="2" t="n"/>
-      <c r="J5" s="2" t="n"/>
+      <c r="B5" s="34" t="n"/>
+      <c r="C5" s="34" t="n"/>
+      <c r="D5" s="34" t="n"/>
+      <c r="E5" s="34" t="n"/>
+      <c r="F5" s="34" t="n"/>
+      <c r="G5" s="34" t="n"/>
+      <c r="H5" s="34" t="n"/>
+      <c r="I5" s="34" t="n"/>
+      <c r="J5" s="35" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
@@ -3405,6 +3457,7 @@
       <c r="I13" s="5" t="n"/>
       <c r="J13" s="5" t="n"/>
     </row>
+    <row r="14"/>
     <row r="15" ht="32" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
@@ -3463,15 +3516,15 @@
           <t>MANO DE OBRA</t>
         </is>
       </c>
-      <c r="B16" s="2" t="n"/>
-      <c r="C16" s="2" t="n"/>
-      <c r="D16" s="2" t="n"/>
-      <c r="E16" s="2" t="n"/>
-      <c r="F16" s="2" t="n"/>
-      <c r="G16" s="2" t="n"/>
-      <c r="H16" s="2" t="n"/>
-      <c r="I16" s="2" t="n"/>
-      <c r="J16" s="2" t="n"/>
+      <c r="B16" s="34" t="n"/>
+      <c r="C16" s="34" t="n"/>
+      <c r="D16" s="34" t="n"/>
+      <c r="E16" s="34" t="n"/>
+      <c r="F16" s="34" t="n"/>
+      <c r="G16" s="34" t="n"/>
+      <c r="H16" s="34" t="n"/>
+      <c r="I16" s="34" t="n"/>
+      <c r="J16" s="35" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
@@ -3597,15 +3650,15 @@
           <t>MATERIALES</t>
         </is>
       </c>
-      <c r="B20" s="2" t="n"/>
-      <c r="C20" s="2" t="n"/>
-      <c r="D20" s="2" t="n"/>
-      <c r="E20" s="2" t="n"/>
-      <c r="F20" s="2" t="n"/>
-      <c r="G20" s="2" t="n"/>
-      <c r="H20" s="2" t="n"/>
-      <c r="I20" s="2" t="n"/>
-      <c r="J20" s="2" t="n"/>
+      <c r="B20" s="34" t="n"/>
+      <c r="C20" s="34" t="n"/>
+      <c r="D20" s="34" t="n"/>
+      <c r="E20" s="34" t="n"/>
+      <c r="F20" s="34" t="n"/>
+      <c r="G20" s="34" t="n"/>
+      <c r="H20" s="34" t="n"/>
+      <c r="I20" s="34" t="n"/>
+      <c r="J20" s="35" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
@@ -4198,15 +4251,15 @@
           <t>EQUIPOS</t>
         </is>
       </c>
-      <c r="B36" s="2" t="n"/>
-      <c r="C36" s="2" t="n"/>
-      <c r="D36" s="2" t="n"/>
-      <c r="E36" s="2" t="n"/>
-      <c r="F36" s="2" t="n"/>
-      <c r="G36" s="2" t="n"/>
-      <c r="H36" s="2" t="n"/>
-      <c r="I36" s="2" t="n"/>
-      <c r="J36" s="2" t="n"/>
+      <c r="B36" s="34" t="n"/>
+      <c r="C36" s="34" t="n"/>
+      <c r="D36" s="34" t="n"/>
+      <c r="E36" s="34" t="n"/>
+      <c r="F36" s="34" t="n"/>
+      <c r="G36" s="34" t="n"/>
+      <c r="H36" s="34" t="n"/>
+      <c r="I36" s="34" t="n"/>
+      <c r="J36" s="35" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="n">

--- a/entregables/COTIZACION_PRECIOS_ACU_TAPA_REGISTRO_HOGAR_REFUGIO.xlsx
+++ b/entregables/COTIZACION_PRECIOS_ACU_TAPA_REGISTRO_HOGAR_REFUGIO.xlsx
@@ -710,7 +710,6 @@
       <c r="M3" s="34" t="n"/>
       <c r="N3" s="35" t="n"/>
     </row>
-    <row r="4"/>
     <row r="5" ht="42" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
@@ -1981,7 +1980,7 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Jornal basico 2026 S/ 89.30 por dia (convenio CAPECO-FTCCP 2026, R.M. 197-2025-TR); costo hora-hombre 2026 de la hoja COSTO HORA HOMBRE 2026 de la planilla</t>
+          <t>Jornal basico 2026 S/ 89.30 por dia; costo hora-hombre en edificacion 2026 de la tabla oficial CAPECO - FTCCP (Exp. N° 339-2025-MTPE/2.14-NC)</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -1990,7 +1989,7 @@
         </is>
       </c>
       <c r="F26" s="6" t="n">
-        <v>29.3</v>
+        <v>28.95</v>
       </c>
       <c r="G26" s="18" t="n">
         <v>1</v>
@@ -2003,7 +2002,7 @@
         <v/>
       </c>
       <c r="J26" s="9" t="n">
-        <v>29.3</v>
+        <v>28.95</v>
       </c>
       <c r="K26" s="10">
         <f>I26/J26-1</f>
@@ -2011,7 +2010,7 @@
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>FTCCP - tablas salariales 2026</t>
+          <t>CAPECO - FTCCP 2026</t>
         </is>
       </c>
       <c r="M26" s="11" t="inlineStr">
@@ -2021,7 +2020,7 @@
       </c>
       <c r="N26" s="12" t="inlineStr">
         <is>
-          <t>JORNAL OFICIAL 2026; costo hh 2026 = costo CAPECO 2024-2025 x jornal 2026 / jornal 2024-2025</t>
+          <t>TABLA OFICIAL CAPECO - FTCCP 2026</t>
         </is>
       </c>
     </row>
@@ -2041,7 +2040,7 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Jornal basico 2026 S/ 69.75 por dia (convenio CAPECO-FTCCP 2026, R.M. 197-2025-TR); costo hora-hombre 2026 de la hoja COSTO HORA HOMBRE 2026 de la planilla</t>
+          <t>Jornal basico 2026 S/ 69.75 por dia; costo hora-hombre en edificacion 2026 de la tabla oficial CAPECO - FTCCP (Exp. N° 339-2025-MTPE/2.14-NC)</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -2050,7 +2049,7 @@
         </is>
       </c>
       <c r="F27" s="6" t="n">
-        <v>22.95</v>
+        <v>22.68</v>
       </c>
       <c r="G27" s="18" t="n">
         <v>1</v>
@@ -2063,7 +2062,7 @@
         <v/>
       </c>
       <c r="J27" s="9" t="n">
-        <v>22.95</v>
+        <v>22.68</v>
       </c>
       <c r="K27" s="10">
         <f>I27/J27-1</f>
@@ -2071,7 +2070,7 @@
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>FTCCP - tablas salariales 2026</t>
+          <t>CAPECO - FTCCP 2026</t>
         </is>
       </c>
       <c r="M27" s="11" t="inlineStr">
@@ -2081,7 +2080,7 @@
       </c>
       <c r="N27" s="12" t="inlineStr">
         <is>
-          <t>JORNAL OFICIAL 2026; costo hh 2026 = costo CAPECO 2024-2025 x jornal 2026 / jornal 2024-2025</t>
+          <t>TABLA OFICIAL CAPECO - FTCCP 2026</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2100,7 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Jornal basico 2026 S/ 62.80 por dia (convenio CAPECO-FTCCP 2026, R.M. 197-2025-TR); costo hora-hombre 2026 de la hoja COSTO HORA HOMBRE 2026 de la planilla</t>
+          <t>Jornal basico 2026 S/ 62.80 por dia; costo hora-hombre en edificacion 2026 de la tabla oficial CAPECO - FTCCP (Exp. N° 339-2025-MTPE/2.14-NC)</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -2110,7 +2109,7 @@
         </is>
       </c>
       <c r="F28" s="6" t="n">
-        <v>20.79</v>
+        <v>20.54</v>
       </c>
       <c r="G28" s="18" t="n">
         <v>1</v>
@@ -2123,7 +2122,7 @@
         <v/>
       </c>
       <c r="J28" s="9" t="n">
-        <v>20.79</v>
+        <v>20.54</v>
       </c>
       <c r="K28" s="10">
         <f>I28/J28-1</f>
@@ -2131,7 +2130,7 @@
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>FTCCP - tablas salariales 2026</t>
+          <t>CAPECO - FTCCP 2026</t>
         </is>
       </c>
       <c r="M28" s="11" t="inlineStr">
@@ -2141,11 +2140,10 @@
       </c>
       <c r="N28" s="12" t="inlineStr">
         <is>
-          <t>JORNAL OFICIAL 2026; costo hh 2026 = costo CAPECO 2024-2025 x jornal 2026 / jornal 2024-2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="29"/>
+          <t>TABLA OFICIAL CAPECO - FTCCP 2026</t>
+        </is>
+      </c>
+    </row>
     <row r="30">
       <c r="A30" s="19" t="inlineStr">
         <is>
@@ -2269,7 +2267,7 @@
     <row r="36" ht="28" customHeight="1">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>6. Mano de obra 2026: jornal basico oficial (R.M. 197-2025-TR) y costo hora-hombre 29.30 / 22.95 / 20.79 de la hoja COSTO HORA HOMBRE 2026 de la planilla (costo CAPECO 2024-2025 llevado al jornal 2026).</t>
+          <t>6. Mano de obra 2026: costo hora-hombre 28.95 / 22.68 / 20.54 de la tabla oficial CAPECO - FTCCP 2026 (hoja COSTO HORA HOMBRE 2026 de la planilla).</t>
         </is>
       </c>
       <c r="B36" s="34" t="n"/>
@@ -2388,7 +2386,6 @@
       <c r="G3" s="34" t="n"/>
       <c r="H3" s="35" t="n"/>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="19" t="inlineStr">
         <is>
@@ -2611,7 +2608,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="19" t="inlineStr">
         <is>
@@ -3087,7 +3083,6 @@
       <c r="G31" s="5" t="n"/>
       <c r="H31" s="3" t="inlineStr"/>
     </row>
-    <row r="32"/>
     <row r="33">
       <c r="A33" s="19" t="inlineStr">
         <is>
@@ -3245,7 +3240,6 @@
       <c r="I3" s="34" t="n"/>
       <c r="J3" s="35" t="n"/>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="19" t="inlineStr">
         <is>
@@ -3457,7 +3451,6 @@
       <c r="I13" s="5" t="n"/>
       <c r="J13" s="5" t="n"/>
     </row>
-    <row r="14"/>
     <row r="15" ht="32" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
